--- a/output/pdf_financials_xlsx/EMPR.xlsx
+++ b/output/pdf_financials_xlsx/EMPR.xlsx
@@ -2859,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>0</v>
+        <v>0.729598</v>
       </c>
       <c r="E108" s="3" t="n">
         <v>0</v>
@@ -4854,7 +4854,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -6352,7 +6356,11 @@
           <t>Impairment charges</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -7492,7 +7500,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E101" s="5" t="n">
         <v>19.107132</v>
       </c>
